--- a/public/sampleFiles/service_user_sample_file.xlsx
+++ b/public/sampleFiles/service_user_sample_file.xlsx
@@ -1,31 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Thirdex\thirdxui\public\sampleFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61669399-58EF-4C12-BE48-7B1AAC59663E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="80">
   <si>
     <t>personalInfo_title</t>
   </si>
@@ -42,9 +28,6 @@
     <t>personalInfo_preferred_name</t>
   </si>
   <si>
-    <t>personalInfo_profile_image</t>
-  </si>
-  <si>
     <t>personalInfo_dob</t>
   </si>
   <si>
@@ -84,16 +67,7 @@
     <t>contactInfo_other_id</t>
   </si>
   <si>
-    <t>demo, deo</t>
-  </si>
-  <si>
-    <t>otherInfo_file</t>
-  </si>
-  <si>
-    <t>otherInfo_notes</t>
-  </si>
-  <si>
-    <t>otherInfo_restrict_access</t>
+    <t>otherInfo_tags</t>
   </si>
   <si>
     <t>emergencyContact_title</t>
@@ -133,9 +107,6 @@
   </si>
   <si>
     <t>emergencyContact_postcode</t>
-  </si>
-  <si>
-    <t>riskAssessment_notes</t>
   </si>
   <si>
     <t>riskAssessment_key_indicators</t>
@@ -203,21 +174,18 @@
     <t>Mrs</t>
   </si>
   <si>
+    <t>Male</t>
+  </si>
+  <si>
     <t>aman</t>
   </si>
   <si>
-    <t>Male</t>
-  </si>
-  <si>
     <t>asati</t>
   </si>
   <si>
     <t>ammy</t>
   </si>
   <si>
-    <t>uploads/profileImage-1751965801943.png</t>
-  </si>
-  <si>
     <t>Arabic or North African</t>
   </si>
   <si>
@@ -239,10 +207,7 @@
     <t>english</t>
   </si>
   <si>
-    <t>uploads/file-1751965801935.png</t>
-  </si>
-  <si>
-    <t>lorem dsrs ddff asad</t>
+    <t>demo, deo</t>
   </si>
   <si>
     <t>Mr</t>
@@ -263,52 +228,44 @@
     <t>Mahalakshmi nagar indore</t>
   </si>
   <si>
+    <t>phone, email</t>
+  </si>
+  <si>
+    <t>Galaxy Inn</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>serma ddfs aa</t>
+  </si>
+  <si>
+    <t>xyz@gmail.com</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>riskAssessment_notes</t>
+  </si>
+  <si>
     <t>and sf sdfe sffg</t>
-  </si>
-  <si>
-    <t>phone, email</t>
-  </si>
-  <si>
-    <t>Galaxy Inn</t>
-  </si>
-  <si>
-    <t>Sharma</t>
-  </si>
-  <si>
-    <t>serma ddfs aa</t>
-  </si>
-  <si>
-    <t>xyz@gmail.com</t>
-  </si>
-  <si>
-    <t>Parent</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>otherInfo_tags</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -328,20 +285,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -368,39 +319,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -435,7 +386,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -479,178 +430,210 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="19.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" customWidth="1"/>
-    <col min="3" max="3" width="21.90625" customWidth="1"/>
-    <col min="4" max="4" width="20.453125" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" customWidth="1"/>
-    <col min="6" max="6" width="20.453125" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" customWidth="1"/>
-    <col min="8" max="8" width="21.08984375" customWidth="1"/>
-    <col min="9" max="9" width="21.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.81640625" customWidth="1"/>
-    <col min="11" max="11" width="19.54296875" customWidth="1"/>
-    <col min="12" max="12" width="20.54296875" customWidth="1"/>
-    <col min="13" max="13" width="19.1796875" customWidth="1"/>
-    <col min="14" max="14" width="17.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.6328125" customWidth="1"/>
-    <col min="16" max="17" width="16.1796875" customWidth="1"/>
-    <col min="18" max="18" width="18.6328125" customWidth="1"/>
-    <col min="19" max="19" width="17.90625" customWidth="1"/>
-    <col min="20" max="20" width="25.81640625" customWidth="1"/>
-    <col min="22" max="22" width="14" customWidth="1"/>
-    <col min="29" max="29" width="16.36328125" customWidth="1"/>
-    <col min="40" max="40" width="13.6328125" customWidth="1"/>
-    <col min="41" max="41" width="14.81640625" customWidth="1"/>
-    <col min="44" max="44" width="15.1796875" customWidth="1"/>
-    <col min="46" max="46" width="19.54296875" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AZ16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:57" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -708,300 +691,2280 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
         <v>20</v>
       </c>
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="B2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="C2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="D2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="E2" t="s">
         <v>56</v>
       </c>
+      <c r="F2" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2">
+        <v>9384840388</v>
+      </c>
+      <c r="I2">
+        <v>9384840388</v>
+      </c>
+      <c r="J2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2">
+        <v>88484</v>
+      </c>
+      <c r="P2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>63</v>
+      </c>
+      <c r="R2">
+        <v>8374</v>
+      </c>
+      <c r="S2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2">
+        <v>9384840388</v>
+      </c>
+      <c r="Z2">
+        <v>9384840388</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF2">
+        <v>476522</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>45847</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM2">
+        <v>9384840388</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO2">
+        <v>9384840388</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV2">
+        <v>9384840388</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:57" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W3" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G4" t="s">
         <v>57</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H4">
+        <v>9384840388</v>
+      </c>
+      <c r="I4">
+        <v>9384840388</v>
+      </c>
+      <c r="J4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O4">
+        <v>88484</v>
+      </c>
+      <c r="P4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4">
+        <v>8374</v>
+      </c>
+      <c r="S4" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U4" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4">
+        <v>9384840388</v>
+      </c>
+      <c r="W4">
+        <v>9384840388</v>
+      </c>
+      <c r="X4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC4">
+        <v>476522</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ4">
+        <v>9384840388</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL4">
+        <v>9384840388</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS4">
+        <v>9384840388</v>
+      </c>
+      <c r="AT4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" t="s">
+        <v>22</v>
+      </c>
+      <c r="U5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" t="s">
+        <v>24</v>
+      </c>
+      <c r="W5" t="s">
+        <v>25</v>
+      </c>
+      <c r="X5" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6">
+        <v>9384840388</v>
+      </c>
+      <c r="I6">
+        <v>9384840388</v>
+      </c>
+      <c r="J6" t="s">
         <v>58</v>
       </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="K6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N6" t="s">
         <v>61</v>
       </c>
-      <c r="F2" t="s">
+      <c r="O6">
+        <v>88484</v>
+      </c>
+      <c r="P6" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="2">
+      <c r="Q6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6">
+        <v>8374</v>
+      </c>
+      <c r="S6" t="s">
+        <v>64</v>
+      </c>
+      <c r="T6" t="s">
+        <v>66</v>
+      </c>
+      <c r="U6" t="s">
+        <v>67</v>
+      </c>
+      <c r="V6">
+        <v>9384840388</v>
+      </c>
+      <c r="W6">
+        <v>9384840388</v>
+      </c>
+      <c r="X6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC6">
+        <v>476522</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ6">
+        <v>9384840388</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL6">
+        <v>9384840388</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS6">
+        <v>9384840388</v>
+      </c>
+      <c r="AT6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S7" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" t="s">
+        <v>25</v>
+      </c>
+      <c r="U7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V7" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" t="s">
+        <v>28</v>
+      </c>
+      <c r="X7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="1">
         <v>37439</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8">
+        <v>9384840388</v>
+      </c>
+      <c r="I8">
+        <v>9384840388</v>
+      </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8">
+        <v>88484</v>
+      </c>
+      <c r="P8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q8" t="s">
         <v>63</v>
       </c>
-      <c r="I2">
-        <v>9384840388</v>
-      </c>
-      <c r="J2">
-        <v>9384840388</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="R8">
+        <v>8374</v>
+      </c>
+      <c r="S8" t="s">
         <v>64</v>
       </c>
-      <c r="L2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="T8">
+        <v>9384840388</v>
+      </c>
+      <c r="U8" t="s">
+        <v>68</v>
+      </c>
+      <c r="V8" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" t="s">
+        <v>70</v>
+      </c>
+      <c r="X8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z8">
+        <v>476522</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>45847</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG8">
+        <v>9384840388</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI8">
+        <v>9384840388</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP8">
+        <v>9384840388</v>
+      </c>
+      <c r="AQ8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" t="s">
+        <v>13</v>
+      </c>
+      <c r="O9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R9" t="s">
+        <v>17</v>
+      </c>
+      <c r="S9" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>23</v>
+      </c>
+      <c r="V9" t="s">
+        <v>24</v>
+      </c>
+      <c r="W9" t="s">
+        <v>25</v>
+      </c>
+      <c r="X9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>45</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>48</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>49</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10">
+        <v>9384840388</v>
+      </c>
+      <c r="I10">
+        <v>9384840388</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O10">
+        <v>88484</v>
+      </c>
+      <c r="P10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>63</v>
+      </c>
+      <c r="R10">
+        <v>8374</v>
+      </c>
+      <c r="S10" t="s">
+        <v>64</v>
+      </c>
+      <c r="T10" t="s">
         <v>66</v>
       </c>
-      <c r="N2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="U10" t="s">
         <v>67</v>
       </c>
-      <c r="P2">
+      <c r="V10">
+        <v>9384840388</v>
+      </c>
+      <c r="W10">
+        <v>9384840388</v>
+      </c>
+      <c r="X10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC10">
+        <v>476522</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ10">
+        <v>9384840388</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL10">
+        <v>9384840388</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AS10">
+        <v>9384840388</v>
+      </c>
+      <c r="AT10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" t="s">
+        <v>14</v>
+      </c>
+      <c r="P11" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>16</v>
+      </c>
+      <c r="R11" t="s">
+        <v>17</v>
+      </c>
+      <c r="S11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T11" t="s">
+        <v>25</v>
+      </c>
+      <c r="U11" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" t="s">
+        <v>28</v>
+      </c>
+      <c r="X11" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12">
+        <v>9384840388</v>
+      </c>
+      <c r="I12">
+        <v>9384840388</v>
+      </c>
+      <c r="J12" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12" t="s">
+        <v>60</v>
+      </c>
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+      <c r="O12">
         <v>88484</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="P12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>63</v>
+      </c>
+      <c r="R12">
+        <v>8374</v>
+      </c>
+      <c r="S12" t="s">
+        <v>64</v>
+      </c>
+      <c r="T12">
+        <v>9384840388</v>
+      </c>
+      <c r="U12" t="s">
         <v>68</v>
       </c>
-      <c r="R2" t="s">
+      <c r="V12" t="s">
         <v>69</v>
       </c>
-      <c r="S2">
+      <c r="W12" t="s">
+        <v>70</v>
+      </c>
+      <c r="X12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z12">
+        <v>476522</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>45847</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG12">
+        <v>9384840388</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI12">
+        <v>9384840388</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP12">
+        <v>9384840388</v>
+      </c>
+      <c r="AQ12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AR12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" t="s">
+        <v>13</v>
+      </c>
+      <c r="O13" t="s">
+        <v>14</v>
+      </c>
+      <c r="P13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>16</v>
+      </c>
+      <c r="R13" t="s">
+        <v>17</v>
+      </c>
+      <c r="S13" t="s">
+        <v>18</v>
+      </c>
+      <c r="T13" t="s">
+        <v>25</v>
+      </c>
+      <c r="U13" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" t="s">
+        <v>28</v>
+      </c>
+      <c r="X13" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>9384840388</v>
+      </c>
+      <c r="I14">
+        <v>9384840388</v>
+      </c>
+      <c r="J14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14">
+        <v>88484</v>
+      </c>
+      <c r="P14" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>63</v>
+      </c>
+      <c r="R14">
         <v>8374</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" s="1" t="s">
+      <c r="S14" t="s">
+        <v>64</v>
+      </c>
+      <c r="T14">
+        <v>9384840388</v>
+      </c>
+      <c r="U14" t="s">
+        <v>68</v>
+      </c>
+      <c r="V14" t="s">
+        <v>69</v>
+      </c>
+      <c r="W14" t="s">
         <v>70</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="X14" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z14">
+        <v>476522</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s">
         <v>71</v>
       </c>
-      <c r="W2" t="b">
+      <c r="AC14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>45847</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG14">
+        <v>9384840388</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI14">
+        <v>9384840388</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>45842</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AP14">
+        <v>9384840388</v>
+      </c>
+      <c r="AQ14" t="b">
         <v>1</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AR14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>16</v>
+      </c>
+      <c r="R15" t="s">
+        <v>17</v>
+      </c>
+      <c r="S15" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U15" t="s">
+        <v>29</v>
+      </c>
+      <c r="V15" t="s">
+        <v>30</v>
+      </c>
+      <c r="W15" t="s">
+        <v>31</v>
+      </c>
+      <c r="X15" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>49</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="1">
+        <v>37439</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16">
+        <v>9384840388</v>
+      </c>
+      <c r="I16">
+        <v>9384840388</v>
+      </c>
+      <c r="J16" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" t="s">
+        <v>61</v>
+      </c>
+      <c r="O16">
+        <v>88484</v>
+      </c>
+      <c r="P16" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16">
+        <v>8374</v>
+      </c>
+      <c r="S16" t="s">
+        <v>64</v>
+      </c>
+      <c r="T16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U16" t="s">
+        <v>60</v>
+      </c>
+      <c r="V16" t="s">
+        <v>60</v>
+      </c>
+      <c r="W16">
+        <v>476522</v>
+      </c>
+      <c r="X16" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z16" t="s">
         <v>72</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA16" s="1">
+        <v>45847</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>45862</v>
+      </c>
+      <c r="AC16" t="s">
         <v>73</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AD16" t="s">
         <v>74</v>
       </c>
-      <c r="AC2">
-        <v>9384840388</v>
-      </c>
-      <c r="AD2">
-        <v>9384840388</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="AE16">
+        <v>9384840388</v>
+      </c>
+      <c r="AF16" t="s">
         <v>75</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AH16" t="s">
         <v>76</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI16" s="1">
+        <v>45840</v>
+      </c>
+      <c r="AJ16" t="s">
         <v>77</v>
       </c>
-      <c r="AH2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ2">
-        <v>476522</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>45847</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>45862</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AR2">
-        <v>9384840388</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AT2">
-        <v>9384840388</v>
-      </c>
-      <c r="AU2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW2" s="2">
-        <v>45840</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY2" s="2">
+      <c r="AK16" s="1">
         <v>45842</v>
       </c>
-      <c r="AZ2" t="s">
-        <v>85</v>
-      </c>
-      <c r="BA2">
-        <v>9384840388</v>
-      </c>
-      <c r="BB2" t="b">
+      <c r="AL16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM16">
+        <v>9384840388</v>
+      </c>
+      <c r="AN16" t="b">
         <v>1</v>
       </c>
-      <c r="BC2" t="b">
+      <c r="AO16" t="b">
         <v>0</v>
       </c>
-      <c r="BD2" t="b">
+      <c r="AP16" t="b">
         <v>0</v>
       </c>
-      <c r="BE2" t="b">
+      <c r="AQ16" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AS2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="AU2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="AN2" r:id="rId1"/>
+    <hyperlink ref="AP2" r:id="rId2"/>
+    <hyperlink ref="AK4" r:id="rId3"/>
+    <hyperlink ref="AM4" r:id="rId4"/>
+    <hyperlink ref="AK6" r:id="rId5"/>
+    <hyperlink ref="AM6" r:id="rId6"/>
+    <hyperlink ref="AH8" r:id="rId7"/>
+    <hyperlink ref="AJ8" r:id="rId8"/>
+    <hyperlink ref="AK10" r:id="rId9"/>
+    <hyperlink ref="AM10" r:id="rId10"/>
+    <hyperlink ref="AH12" r:id="rId11"/>
+    <hyperlink ref="AJ12" r:id="rId12"/>
+    <hyperlink ref="AH14" r:id="rId13"/>
+    <hyperlink ref="AJ14" r:id="rId14"/>
+    <hyperlink ref="AF16" r:id="rId15"/>
+    <hyperlink ref="AG16" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>